--- a/ResourcesPH/dsrProfileData.xlsx
+++ b/ResourcesPH/dsrProfileData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="646">
   <si>
     <t>DT Code*</t>
   </si>
@@ -1777,6 +1777,186 @@
   </si>
   <si>
     <t>EMPD14D95</t>
+  </si>
+  <si>
+    <t>AUTODSR_97C5E</t>
+  </si>
+  <si>
+    <t>Father_AB75</t>
+  </si>
+  <si>
+    <t>03322233000</t>
+  </si>
+  <si>
+    <t>EMP8A7095</t>
+  </si>
+  <si>
+    <t>AUTODSR_F9726</t>
+  </si>
+  <si>
+    <t>Father_666D</t>
+  </si>
+  <si>
+    <t>03329748400</t>
+  </si>
+  <si>
+    <t>EMP506E0C</t>
+  </si>
+  <si>
+    <t>AUTODSR_0C02E</t>
+  </si>
+  <si>
+    <t>Father_4B63</t>
+  </si>
+  <si>
+    <t>03333164300</t>
+  </si>
+  <si>
+    <t>EMP31BC2F</t>
+  </si>
+  <si>
+    <t>AUTODSR_0EA31</t>
+  </si>
+  <si>
+    <t>Father_7BB6</t>
+  </si>
+  <si>
+    <t>03542148800</t>
+  </si>
+  <si>
+    <t>EMP026985</t>
+  </si>
+  <si>
+    <t>AUTODSR_292DC</t>
+  </si>
+  <si>
+    <t>Father_7078</t>
+  </si>
+  <si>
+    <t>03544624000</t>
+  </si>
+  <si>
+    <t>EMPB6E61A</t>
+  </si>
+  <si>
+    <t>AUTODSR_E0210</t>
+  </si>
+  <si>
+    <t>Father_734B</t>
+  </si>
+  <si>
+    <t>03547374900</t>
+  </si>
+  <si>
+    <t>EMPDB33D1</t>
+  </si>
+  <si>
+    <t>AUTODSR_14C16</t>
+  </si>
+  <si>
+    <t>Father_B10F</t>
+  </si>
+  <si>
+    <t>03600277300</t>
+  </si>
+  <si>
+    <t>EMP940916</t>
+  </si>
+  <si>
+    <t>AUTODSR_28C43</t>
+  </si>
+  <si>
+    <t>Father_52A2</t>
+  </si>
+  <si>
+    <t>03605411300</t>
+  </si>
+  <si>
+    <t>EMPAC03AB</t>
+  </si>
+  <si>
+    <t>AUTODSR_10DA0</t>
+  </si>
+  <si>
+    <t>Father_C724</t>
+  </si>
+  <si>
+    <t>03608109600</t>
+  </si>
+  <si>
+    <t>EMP7F7BE5</t>
+  </si>
+  <si>
+    <t>AUTODSR_00DE3</t>
+  </si>
+  <si>
+    <t>Father_55D6</t>
+  </si>
+  <si>
+    <t>03954077700</t>
+  </si>
+  <si>
+    <t>EMPAFDAE8</t>
+  </si>
+  <si>
+    <t>AUTODSR_DF8FC</t>
+  </si>
+  <si>
+    <t>Father_8D19</t>
+  </si>
+  <si>
+    <t>03955796000</t>
+  </si>
+  <si>
+    <t>EMPEA1E32</t>
+  </si>
+  <si>
+    <t>AUTODSR_9F0BF</t>
+  </si>
+  <si>
+    <t>Father_793F</t>
+  </si>
+  <si>
+    <t>03956649900</t>
+  </si>
+  <si>
+    <t>EMP730BB8</t>
+  </si>
+  <si>
+    <t>AUTODSR_3F517</t>
+  </si>
+  <si>
+    <t>Father_4BA8</t>
+  </si>
+  <si>
+    <t>03087594800</t>
+  </si>
+  <si>
+    <t>EMPF09E67</t>
+  </si>
+  <si>
+    <t>AUTODSR_332F0</t>
+  </si>
+  <si>
+    <t>Father_8980</t>
+  </si>
+  <si>
+    <t>03092866800</t>
+  </si>
+  <si>
+    <t>EMP6469F4</t>
+  </si>
+  <si>
+    <t>AUTODSR_988AA</t>
+  </si>
+  <si>
+    <t>Father_3FF1</t>
+  </si>
+  <si>
+    <t>03096128600</t>
+  </si>
+  <si>
+    <t>EMPC61BC4</t>
   </si>
 </sst>
 </file>
@@ -2193,19 +2373,19 @@
         <v>35</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>574</v>
+        <v>634</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>575</v>
+        <v>635</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>576</v>
+        <v>636</v>
       </c>
       <c r="F2" t="s" s="0">
         <v>28</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>577</v>
+        <v>637</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>23</v>
@@ -2255,19 +2435,19 @@
         <v>36</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>578</v>
+        <v>638</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>579</v>
+        <v>639</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>580</v>
+        <v>640</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>27</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>581</v>
+        <v>641</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>23</v>
@@ -2317,19 +2497,19 @@
         <v>21</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>582</v>
+        <v>642</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>583</v>
+        <v>643</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>584</v>
+        <v>644</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>28</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>585</v>
+        <v>645</v>
       </c>
       <c r="H4" t="s" s="0">
         <v>23</v>
